--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.7468483873848</v>
+        <v>3.37136286295003</v>
       </c>
       <c r="D2" t="n">
-        <v>20.47103122317425</v>
+        <v>3.326542573765817</v>
       </c>
       <c r="E2" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F2" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.554591178801606</v>
+        <v>0.740121066555261</v>
       </c>
       <c r="D3" t="n">
-        <v>4.872637040311738</v>
+        <v>0.7918035190506575</v>
       </c>
       <c r="E3" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F3" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.81449210123669</v>
+        <v>2.407354966450962</v>
       </c>
       <c r="D4" t="n">
-        <v>15.13820470213767</v>
+        <v>2.459958264097371</v>
       </c>
       <c r="E4" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F4" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.849893691617686</v>
+        <v>1.113107724887874</v>
       </c>
       <c r="D5" t="n">
-        <v>6.926277365378714</v>
+        <v>1.125520071874041</v>
       </c>
       <c r="E5" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F5" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.84562144998715</v>
+        <v>3.549913485622911</v>
       </c>
       <c r="D6" t="n">
-        <v>21.79046189585987</v>
+        <v>3.540950058077228</v>
       </c>
       <c r="E6" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F6" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.37386836315755</v>
+        <v>3.635753609013102</v>
       </c>
       <c r="D7" t="n">
-        <v>22.1778011404914</v>
+        <v>3.603892685329853</v>
       </c>
       <c r="E7" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F7" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.92272375389068</v>
+        <v>2.424942610007236</v>
       </c>
       <c r="D8" t="n">
-        <v>14.93161313059545</v>
+        <v>2.42638713372176</v>
       </c>
       <c r="E8" t="n">
-        <v>6.65108502690004</v>
+        <v>1.080801316871256</v>
       </c>
       <c r="F8" t="n">
-        <v>6.492756629754578</v>
+        <v>1.055072952335119</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
